--- a/artfynd/A 50816-2023 artfynd.xlsx
+++ b/artfynd/A 50816-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50816-2023 artfynd.xlsx
+++ b/artfynd/A 50816-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112940176</v>
+        <v>112600953</v>
       </c>
       <c r="B2" t="n">
-        <v>107794</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220228</v>
+        <v>809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Praktvaxing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Hygrocybe splendidissima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.D.Orton) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NVI sävsjö m.fl., Sm</t>
+          <t>Karstorp, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480922</v>
+        <v>480915</v>
       </c>
       <c r="R2" t="n">
-        <v>6364929</v>
+        <v>6364868</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,21 +765,236 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ängssvampar Jönköpings län 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>112600962</v>
+      </c>
+      <c r="B3" t="n">
+        <v>88980</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3295</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Hagfingersvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Clavulinopsis helvola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pers.) Corner</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Karstorp K32, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>480950</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6364873</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ängssvampar Jönköpings län 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112940176</v>
+      </c>
+      <c r="B4" t="n">
+        <v>109866</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NVI sävsjö m.fl., Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>480923</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6364928</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Julia Falk</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Julia Falk, Julia Svensson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>EWN0078 NVI Sävsjö</t>
         </is>

--- a/artfynd/A 50816-2023 artfynd.xlsx
+++ b/artfynd/A 50816-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>Ängssvampar Jönköpings län 2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112600953</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Ängssvampar Jönköpings län 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112600962</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,8 +1014,18 @@
           <t>EWN0078 NVI Sävsjö</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112940176</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>